--- a/artfynd/A 27298-2026 artfynd.xlsx
+++ b/artfynd/A 27298-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,58 +675,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2218119</v>
+        <v>99733</v>
       </c>
       <c r="B2" t="n">
-        <v>108193</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219711</v>
+        <v>178</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Skugglosta</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Bromopsis ramosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Huds.) Holub</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Grankullavik SV. Brandlinjen, Öl</t>
+          <t>Älgmaden, Öl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>624711.5606291495</v>
+        <v>624716</v>
       </c>
       <c r="R2" t="n">
-        <v>6356641.775474919</v>
+        <v>6356644</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,22 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2008-05-16</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-08-30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2008-05-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-08-30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,71 +768,84 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Kring skogsväg i blandskog</t>
+          <t>vid kanal</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Karl-göran Bringer</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Karl-göran Bringer, Lissbeth Bringer</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Thomas Gunnarsson, Lennart Johnsson, Ingrid Johnsson, Håkan Lundkvist, Ulla-Britt Andersson, Tommy Knutsson, Sakari Öistämö</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2152943</v>
+        <v>68791322</v>
       </c>
       <c r="B3" t="n">
-        <v>107996</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>7199</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219677</v>
+        <v>102236</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Grenplattnos</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Pseudeuparius sepicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Fabricius, 1792)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Grankullavik SV. Brandlinjen, Öl</t>
+          <t>Sjöstorps naturreservat Öster om och vid Spökbackevägen., Öl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>625000.2758180115</v>
+        <v>625010</v>
       </c>
       <c r="R3" t="n">
-        <v>6356561.463922636</v>
+        <v>6356493</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,22 +869,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2008-05-16</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1997-11-19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2008-05-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1997-11-19</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>i murken bokgren på marken</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,33 +893,38 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Längs skogsväg i blandskog</t>
+          <t>Bokskogsparti litet i barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>Håkan Lundkvist</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>2992</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Karl-göran Bringer</t>
+          <t>Håkan Lundkvist</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Karl-göran Bringer, Lissbeth Bringer</t>
+          <t>Håkan Lundkvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>99733</v>
+        <v>71296415</v>
       </c>
       <c r="B4" t="n">
-        <v>97517</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56689</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -930,46 +932,57 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>178</v>
+        <v>206046</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skugglosta</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bromopsis ramosa</t>
+          <t>Alces alces</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Huds.) Holub</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Älgmaden, Öl</t>
+          <t>Nord Älgmaden, Öl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>624716.3606428212</v>
+        <v>624984</v>
       </c>
       <c r="R4" t="n">
-        <v>6356644.081977142</v>
+        <v>6356570</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -993,22 +1006,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2009-08-30</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-05-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2009-08-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-05-12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,88 +1022,64 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>vid kanal</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Robin Isaksson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Lennart Johnsson, Ingrid Johnsson, Håkan Lundkvist, Ulla-Britt Andersson, Tommy Knutsson, Sakari Öistämö</t>
+          <t>Robin Isaksson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>68791322</v>
+        <v>2152943</v>
       </c>
       <c r="B5" t="n">
-        <v>7111</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111175</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102236</v>
+        <v>219677</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grenplattnos</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudeuparius sepicola</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fabricius, 1792)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sjöstorps naturreservat Öster om och vid Spökbackevägen., Öl</t>
+          <t>Grankullavik SV. Brandlinjen, Öl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>625009.953267272</v>
+        <v>625000</v>
       </c>
       <c r="R5" t="n">
-        <v>6356492.626843181</v>
+        <v>6356561</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1124,27 +1103,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1997-11-19</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-05-16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1997-11-19</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>i murken bokgren på marken</t>
+          <t>2008-05-16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1158,31 +1122,242 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Bokskogsparti litet i barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>Håkan Lundkvist</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>2992</t>
+          <t>Längs skogsväg i blandskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Håkan Lundkvist</t>
+          <t>Karl-göran Bringer</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Håkan Lundkvist</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Karl-göran Bringer, Lissbeth Bringer</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2218119</v>
+      </c>
+      <c r="B6" t="n">
+        <v>111389</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Grankullavik SV. Brandlinjen, Öl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>624712</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6356642</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2008-05-16</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2008-05-16</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Kring skogsväg i blandskog</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Karl-göran Bringer</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Karl-göran Bringer, Lissbeth Bringer</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>4425988</v>
+      </c>
+      <c r="B7" t="n">
+        <v>102559</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Grankullavik västerut. Spökbackevägen, Öl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>625093</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6356639</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2009-06-24</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2009-06-24</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Vägren</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Karl-göran Bringer</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Karl-göran Bringer, Lissbeth Bringer</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27298-2026 artfynd.xlsx
+++ b/artfynd/A 27298-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99733</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -918,6 +928,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68791322</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1035,6 +1050,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71296415</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1141,6 +1161,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2152943</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1252,6 +1277,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2218119</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1358,8 +1388,21 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4425988</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>